--- a/pinnacle_league_inputs_web.xlsx
+++ b/pinnacle_league_inputs_web.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42771EED-3C9F-4BF6-9501-EDE43C520511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E3437FC-A132-4489-8838-190744353AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24855" yWindow="-12810" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>LEAGUE</t>
   </si>
@@ -23,48 +23,6 @@
     <t>LEAGUE URL</t>
   </si>
   <si>
-    <t>https://www.pinnacle.com/en/soccer/finland-veikkausliiga/matchups/#period:0</t>
-  </si>
-  <si>
-    <t>https://www.pinnacle.com/en/soccer/spain-segunda-division/matchups#period:0</t>
-  </si>
-  <si>
-    <t>https://www.pinnacle.com/en/soccer/sweden-superettan/matchups/#period:0</t>
-  </si>
-  <si>
-    <t>Sweden - Superettan</t>
-  </si>
-  <si>
-    <t>https://www.pinnacle.com/en/soccer/norway-1st-division/matchups/#period:0</t>
-  </si>
-  <si>
-    <t>Norway - 1st Division</t>
-  </si>
-  <si>
-    <t>https://www.pinnacle.com/en/soccer/iceland-1-deild/matchups/#period:0</t>
-  </si>
-  <si>
-    <t>Iceland - 1. Deild</t>
-  </si>
-  <si>
-    <t>Finland - Veikkausliiga</t>
-  </si>
-  <si>
-    <t>Spain - Segunda</t>
-  </si>
-  <si>
-    <t>https://www.pinnacle.com/en/soccer/finland-ykkosliiga/matchups/#period:0</t>
-  </si>
-  <si>
-    <t>Finland - Ykkosliiga</t>
-  </si>
-  <si>
-    <t>https://www.pinnacle.com/en/soccer/brazil-serie-b/matchups/#period:0</t>
-  </si>
-  <si>
-    <t>Brazil - Serie B</t>
-  </si>
-  <si>
     <t>https://www.pinnacle.com/en/soccer/poland-ekstraklasa/matchups/#period:0</t>
   </si>
   <si>
@@ -77,10 +35,22 @@
     <t>https://www.pinnacle.com/en/soccer/poland-1st-liga/matchups/#period:0</t>
   </si>
   <si>
-    <t>Romania - Liga 1</t>
-  </si>
-  <si>
-    <t>https://www.pinnacle.com/en/soccer/romania-liga-1/matchups/#period:0</t>
+    <t>https://www.pinnacle.com/en/soccer/turkey-super-league/matchups/#period:0</t>
+  </si>
+  <si>
+    <t>Turkey - Super Lig</t>
+  </si>
+  <si>
+    <t>https://www.pinnacle.com/en/soccer/germany-bundesliga/matchups/#period:0</t>
+  </si>
+  <si>
+    <t>Germany - Bundesliga</t>
+  </si>
+  <si>
+    <t>https://www.pinnacle.com/en/soccer/portugal-primeira-liga/matchups/#period:0</t>
+  </si>
+  <si>
+    <t>Portugal - Primeira Liga</t>
   </si>
 </sst>
 </file>
@@ -431,10 +401,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="69" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="72.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -451,79 +421,39 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
